--- a/outputs/tables/ame_bootstrap_results_retain.xlsx
+++ b/outputs/tables/ame_bootstrap_results_retain.xlsx
@@ -458,25 +458,25 @@
         <v>0.00250516132598715</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000930213661336966</v>
+        <v>0.00109211939897434</v>
       </c>
       <c r="E2" t="n">
-        <v>2.69310313330226</v>
+        <v>2.29385296913493</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00707903675690216</v>
+        <v>0.0217989456602875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00117187136668659</v>
+        <v>0.000646331257276744</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00434909391196301</v>
+        <v>0.00479164397773737</v>
       </c>
       <c r="I2" t="n">
         <v>0.95</v>
       </c>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -493,25 +493,25 @@
         <v>-0.000687830622758916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000846657499013912</v>
+        <v>0.000727801643425796</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.812407170030409</v>
+        <v>-0.945079787840634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.416558033379427</v>
+        <v>0.344618143392669</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00228492412468983</v>
+        <v>-0.00230392090756994</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00079471890128409</v>
+        <v>0.000674093841177462</v>
       </c>
       <c r="I3" t="n">
         <v>0.95</v>
       </c>
       <c r="J3" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -528,25 +528,25 @@
         <v>0.00435877043409529</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000935966821507316</v>
+        <v>0.0010030901141131</v>
       </c>
       <c r="E4" t="n">
-        <v>4.65697109548794</v>
+        <v>4.34534282889345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000320895477015023</v>
+        <v>0.000013905831004459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00302354074297247</v>
+        <v>0.00257670618286975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00628593714501703</v>
+        <v>0.00627364198755122</v>
       </c>
       <c r="I4" t="n">
         <v>0.95</v>
       </c>
       <c r="J4" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -563,25 +563,25 @@
         <v>-0.00691239229896322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00113573854195043</v>
+        <v>0.00116180371451794</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.08625316799796</v>
+        <v>-5.94970752166283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00000000115583626461237</v>
+        <v>0.00000000268622063786837</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00942408809513822</v>
+        <v>-0.00931063600636589</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0052287059942304</v>
+        <v>-0.00492821411002855</v>
       </c>
       <c r="I5" t="n">
         <v>0.95</v>
       </c>
       <c r="J5" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -598,25 +598,25 @@
         <v>-0.0108653400484964</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00128220822336489</v>
+        <v>0.00131455555075108</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.47392790851282</v>
+        <v>-8.26540958447014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0000000000000000237254290321947</v>
+        <v>0.000000000000000139215924167219</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0143019594632439</v>
+        <v>-0.0132409344854957</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00917682299354005</v>
+        <v>-0.00880579959957713</v>
       </c>
       <c r="I6" t="n">
         <v>0.95</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -633,25 +633,25 @@
         <v>0.00852159415176789</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00107481879178954</v>
+        <v>0.0010323669594677</v>
       </c>
       <c r="E7" t="n">
-        <v>7.92840078426589</v>
+        <v>8.25442355900436</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00000000000000221985904297842</v>
+        <v>0.000000000000000152637133689866</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00699317001860099</v>
+        <v>0.00679348992683583</v>
       </c>
       <c r="H7" t="n">
-        <v>0.011212518916043</v>
+        <v>0.011002657660694</v>
       </c>
       <c r="I7" t="n">
         <v>0.95</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -668,25 +668,25 @@
         <v>0.00387726046972584</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00187798849638561</v>
+        <v>0.00205245400552105</v>
       </c>
       <c r="E8" t="n">
-        <v>2.06458158672859</v>
+        <v>1.88908519230935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0389626069743849</v>
+        <v>0.0588804142700608</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000354555677443068</v>
+        <v>0.000242066476282072</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00740518016841889</v>
+        <v>0.0083107775108749</v>
       </c>
       <c r="I8" t="n">
         <v>0.95</v>
       </c>
       <c r="J8" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -703,25 +703,25 @@
         <v>-0.00238778568081743</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0016733507465062</v>
+        <v>0.00151645203824023</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.42694870504758</v>
+        <v>-1.57458701007672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.153594680514828</v>
+        <v>0.115351803155925</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00594659847935241</v>
+        <v>-0.00582399587967302</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000383681653772434</v>
+        <v>0.000294141388629569</v>
       </c>
       <c r="I9" t="n">
         <v>0.95</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -738,25 +738,25 @@
         <v>0.00798060075954467</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00198949839096464</v>
+        <v>0.00190542272254767</v>
       </c>
       <c r="E10" t="n">
-        <v>4.01136326412164</v>
+        <v>4.18836233299144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0000603691376914678</v>
+        <v>0.0000280974669896639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00448194080991698</v>
+        <v>0.00438601971964453</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0116784898305827</v>
+        <v>0.0117071204357964</v>
       </c>
       <c r="I10" t="n">
         <v>0.95</v>
       </c>
       <c r="J10" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -773,25 +773,25 @@
         <v>-0.0137243074408153</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00166396658768567</v>
+        <v>0.00218496434678907</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.24794652872437</v>
+        <v>-6.28125006295136</v>
       </c>
       <c r="F11" t="n">
-        <v>0.000000000000000161139436958969</v>
+        <v>0.000000000335861411281907</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0167646658867874</v>
+        <v>-0.0190059493414001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0111846160668032</v>
+        <v>-0.0101391577574058</v>
       </c>
       <c r="I11" t="n">
         <v>0.95</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -808,25 +808,25 @@
         <v>-0.0172438090787281</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00211389288814028</v>
+        <v>0.0023996562754364</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.15737125351631</v>
+        <v>-7.18594961088422</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000000000000000342394722627333</v>
+        <v>0.0000000000006674165761975</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0226281460558556</v>
+        <v>-0.0232216186349535</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0138827520788223</v>
+        <v>-0.0135954408918826</v>
       </c>
       <c r="I12" t="n">
         <v>0.95</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -843,25 +843,25 @@
         <v>0.0104464346040755</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00177857367078723</v>
+        <v>0.00178742830491171</v>
       </c>
       <c r="E13" t="n">
-        <v>5.87348996314092</v>
+        <v>5.84439363266741</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00000000426714877736158</v>
+        <v>0.00000000508416776852982</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00770324045777415</v>
+        <v>0.00733477019318567</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0140655266540762</v>
+        <v>0.0141680918567823</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
       </c>
       <c r="J13" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -878,25 +878,25 @@
         <v>0.00231682921083476</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00335604259936959</v>
+        <v>0.00317254688929111</v>
       </c>
       <c r="E14" t="n">
-        <v>0.690345590747258</v>
+        <v>0.730274221842139</v>
       </c>
       <c r="F14" t="n">
-        <v>0.489976883920176</v>
+        <v>0.465222581957194</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00218148936409277</v>
+        <v>-0.00288823368847266</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0106377787935817</v>
+        <v>0.00968438858808106</v>
       </c>
       <c r="I14" t="n">
         <v>0.95</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -913,25 +913,25 @@
         <v>0.00210399998609066</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00261371489200546</v>
+        <v>0.00239785592802432</v>
       </c>
       <c r="E15" t="n">
-        <v>0.804984504058243</v>
+        <v>0.877450543004149</v>
       </c>
       <c r="F15" t="n">
-        <v>0.420828621977363</v>
+        <v>0.38024197058747</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.00313030750068823</v>
+        <v>-0.00235857178082196</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0071964725250886</v>
+        <v>0.00701422172022342</v>
       </c>
       <c r="I15" t="n">
         <v>0.95</v>
       </c>
       <c r="J15" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -948,25 +948,25 @@
         <v>0.00986257482305979</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00360094032742184</v>
+        <v>0.00339572689395991</v>
       </c>
       <c r="E16" t="n">
-        <v>2.73888871413792</v>
+        <v>2.90440754838167</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00616472366626185</v>
+        <v>0.00367948854216569</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00329599673490454</v>
+        <v>0.00368416336669017</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0177941261837955</v>
+        <v>0.0174726226376145</v>
       </c>
       <c r="I16" t="n">
         <v>0.95</v>
       </c>
       <c r="J16" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -983,25 +983,25 @@
         <v>-0.0288497543851824</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00361768907789319</v>
+        <v>0.00336513205550228</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.9746362288225</v>
+        <v>-8.57314182901399</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00000000000000152830288501597</v>
+        <v>0.0000000000000000100699363138607</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0361844554022485</v>
+        <v>-0.0358418874412849</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0214722063302412</v>
+        <v>-0.0222297522502873</v>
       </c>
       <c r="I17" t="n">
         <v>0.95</v>
       </c>
       <c r="J17" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v>-0.0349315983597081</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00374766762942674</v>
+        <v>0.00404610709348434</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.32089016790728</v>
+        <v>-8.63338452310378</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0000000000000000000115368268259306</v>
+        <v>0.00000000000000000595627843365829</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0427657022813374</v>
+        <v>-0.0428828440238037</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0282205219749131</v>
+        <v>-0.0280328602069588</v>
       </c>
       <c r="I18" t="n">
         <v>0.95</v>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1053,25 +1053,25 @@
         <v>0.0242044128199862</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00233757908056197</v>
+        <v>0.00293936215741199</v>
       </c>
       <c r="E19" t="n">
-        <v>10.3544787088732</v>
+        <v>8.23457999517058</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000000000000000000000000399356059847022</v>
+        <v>0.000000000000000180188676134068</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0197805134661398</v>
+        <v>0.0180907636323887</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0288846731980314</v>
+        <v>0.0299909790724816</v>
       </c>
       <c r="I19" t="n">
         <v>0.95</v>
       </c>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1088,25 +1088,25 @@
         <v>0.00906109734923069</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00544938783008424</v>
+        <v>0.0052201814979514</v>
       </c>
       <c r="E20" t="n">
-        <v>1.66277344020321</v>
+        <v>1.73578205140695</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0963577950755796</v>
+        <v>0.0826023788944131</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.00239010461365922</v>
+        <v>-0.00169478672511885</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0194404087685528</v>
+        <v>0.019489387540328</v>
       </c>
       <c r="I20" t="n">
         <v>0.95</v>
       </c>
       <c r="J20" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1123,25 +1123,25 @@
         <v>0.000126484178421768</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0047514582395449</v>
+        <v>0.00392231172035752</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0266200757841203</v>
+        <v>0.0322473549884605</v>
       </c>
       <c r="F21" t="n">
-        <v>0.978762760772665</v>
+        <v>0.974274791977822</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.00629287285558535</v>
+        <v>-0.00574941073285848</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0105163177670131</v>
+        <v>0.00897625583139448</v>
       </c>
       <c r="I21" t="n">
         <v>0.95</v>
       </c>
       <c r="J21" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1158,25 +1158,25 @@
         <v>0.0223135358283244</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00553278379416509</v>
+        <v>0.00527572305610029</v>
       </c>
       <c r="E22" t="n">
-        <v>4.03296724731165</v>
+        <v>4.22947444190108</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0000550769585354085</v>
+        <v>0.0000234237886862953</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00990342693350234</v>
+        <v>0.0108271105435205</v>
       </c>
       <c r="H22" t="n">
-        <v>0.032465560972016</v>
+        <v>0.031348258972076</v>
       </c>
       <c r="I22" t="n">
         <v>0.95</v>
       </c>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1193,25 +1193,25 @@
         <v>-0.0490366814132291</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00490865538931612</v>
+        <v>0.00477684562388808</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.98983988975055</v>
+        <v>-10.2654942768102</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0000000000000000000000168854258879365</v>
+        <v>0.00000000000000000000000100803421708049</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.059467229224725</v>
+        <v>-0.0584659994663104</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0425891103960169</v>
+        <v>-0.041496314943436</v>
       </c>
       <c r="I23" t="n">
         <v>0.95</v>
       </c>
       <c r="J23" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1228,25 +1228,25 @@
         <v>-0.0628045477509041</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00547100489595562</v>
+        <v>0.00563988359606504</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.4795268776549</v>
+        <v>-11.1357879433404</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00000000000000000000000000000167192892702215</v>
+        <v>0.0000000000000000000000000000839988519764535</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0738841295229442</v>
+        <v>-0.0743452709812594</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0547004000563214</v>
+        <v>-0.0536908630714764</v>
       </c>
       <c r="I24" t="n">
         <v>0.95</v>
       </c>
       <c r="J24" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1263,25 +1263,25 @@
         <v>0.0428952462862584</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00463417834830771</v>
+        <v>0.00425260181665339</v>
       </c>
       <c r="E25" t="n">
-        <v>9.25627868895522</v>
+        <v>10.0868240516379</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0000000000000000000211681318765906</v>
+        <v>0.00000000000000000000000631806565103899</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0318106421618741</v>
+        <v>0.0336970900283098</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0503166222064027</v>
+        <v>0.0502512007140882</v>
       </c>
       <c r="I25" t="n">
         <v>0.95</v>
       </c>
       <c r="J25" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1298,25 +1298,25 @@
         <v>0.00837398100831876</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0032481589209181</v>
+        <v>0.00262499969597587</v>
       </c>
       <c r="E26" t="n">
-        <v>2.57806998124089</v>
+        <v>3.19008837264098</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00993538744525625</v>
+        <v>0.00142229294191323</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00375915741741344</v>
+        <v>0.00365978320824872</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0143278611042769</v>
+        <v>0.014119748046562</v>
       </c>
       <c r="I26" t="n">
         <v>0.95</v>
       </c>
       <c r="J26" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1333,25 +1333,25 @@
         <v>-0.00169981310883989</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00184070627544785</v>
+        <v>0.00203814177408992</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.923457007515403</v>
+        <v>-0.834001407776893</v>
       </c>
       <c r="F27" t="n">
-        <v>0.355769095159272</v>
+        <v>0.40428019055048</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0043870058317896</v>
+        <v>-0.0064785083536541</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00275247066561664</v>
+        <v>0.00225507546707117</v>
       </c>
       <c r="I27" t="n">
         <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1368,25 +1368,25 @@
         <v>0.0107620080766772</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00271967099538903</v>
+        <v>0.00242102561958056</v>
       </c>
       <c r="E28" t="n">
-        <v>3.95709925756583</v>
+        <v>4.4452268450351</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0000758654127295188</v>
+        <v>0.00000877991737412737</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00493615992269153</v>
+        <v>0.00652046357094983</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0157226342297673</v>
+        <v>0.0154536489402304</v>
       </c>
       <c r="I28" t="n">
         <v>0.95</v>
       </c>
       <c r="J28" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1403,25 +1403,25 @@
         <v>-0.0241952239310903</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0036425536553562</v>
+        <v>0.00357050127888534</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.64237955575819</v>
+        <v>-6.77642214390795</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0000000000308658869675658</v>
+        <v>0.000000000012318839576989</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0316926004265177</v>
+        <v>-0.0323247767520221</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0171181973249759</v>
+        <v>-0.0186868038316418</v>
       </c>
       <c r="I29" t="n">
         <v>0.95</v>
       </c>
       <c r="J29" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1438,25 +1438,25 @@
         <v>-0.029111075963486</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00411634324991815</v>
+        <v>0.00406889715953359</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.07207202996611</v>
+        <v>-7.15453716869632</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00000000000152637149464608</v>
+        <v>0.000000000000839556971613147</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0376191322914062</v>
+        <v>-0.0391163089377771</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0217661452240427</v>
+        <v>-0.022658614259078</v>
       </c>
       <c r="I30" t="n">
         <v>0.95</v>
       </c>
       <c r="J30" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1473,25 +1473,25 @@
         <v>0.0173276133382448</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00254904287972944</v>
+        <v>0.00253130825393029</v>
       </c>
       <c r="E31" t="n">
-        <v>6.79769394074847</v>
+        <v>6.84531933688469</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0000000000106306990960274</v>
+        <v>0.00000000000763054624813875</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0125353118972134</v>
+        <v>0.0136127156610403</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0229709036618256</v>
+        <v>0.0231817246822358</v>
       </c>
       <c r="I31" t="n">
         <v>0.95</v>
       </c>
       <c r="J31" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1508,25 +1508,25 @@
         <v>0.00759232465611811</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00422791396389626</v>
+        <v>0.00447383374355032</v>
       </c>
       <c r="E32" t="n">
-        <v>1.79576138988442</v>
+        <v>1.69705114032535</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0725324737221555</v>
+        <v>0.0896869924098386</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.000553894509193147</v>
+        <v>-0.000773372087884253</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0149650531388291</v>
+        <v>0.0166079980123437</v>
       </c>
       <c r="I32" t="n">
         <v>0.95</v>
       </c>
       <c r="J32" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1543,25 +1543,25 @@
         <v>-0.00088699438224994</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00370696948115171</v>
+        <v>0.00366791907930532</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.239277497902239</v>
+        <v>-0.241824959349412</v>
       </c>
       <c r="F33" t="n">
-        <v>0.810890412755062</v>
+        <v>0.808915798040249</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.00836275794953176</v>
+        <v>-0.00762053384582806</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00465258858820537</v>
+        <v>0.00576244726270444</v>
       </c>
       <c r="I33" t="n">
         <v>0.95</v>
       </c>
       <c r="J33" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1578,25 +1578,25 @@
         <v>0.0119709036945148</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0039324290037731</v>
+        <v>0.00399520745794877</v>
       </c>
       <c r="E34" t="n">
-        <v>3.0441499854235</v>
+        <v>2.99631591613541</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00233338776737888</v>
+        <v>0.00273263171131501</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00602346981368711</v>
+        <v>0.0047580303623965</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0199076755462717</v>
+        <v>0.0202934374591504</v>
       </c>
       <c r="I34" t="n">
         <v>0.95</v>
       </c>
       <c r="J34" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         <v>-0.0353717039255422</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00493256561185166</v>
+        <v>0.00538506830375916</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.1710559390337</v>
+        <v>-6.56847823097253</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0000000000007442148465961</v>
+        <v>0.0000000000508320620258589</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0440394602520537</v>
+        <v>-0.0448613984206448</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0262997167207579</v>
+        <v>-0.0256132236896662</v>
       </c>
       <c r="I35" t="n">
         <v>0.95</v>
       </c>
       <c r="J35" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1648,25 +1648,25 @@
         <v>-0.0435307213056495</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00527707783849591</v>
+        <v>0.00601066716164585</v>
       </c>
       <c r="E36" t="n">
-        <v>-8.24902012778663</v>
+        <v>-7.24224451878149</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000000000000000159698539337968</v>
+        <v>0.000000000000441319248927018</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0503435263227699</v>
+        <v>-0.053821090810471</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0316445866016407</v>
+        <v>-0.0317277707632881</v>
       </c>
       <c r="I36" t="n">
         <v>0.95</v>
       </c>
       <c r="J36" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1683,25 +1683,25 @@
         <v>0.0340266285395732</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00367281773875371</v>
+        <v>0.00405357218297971</v>
       </c>
       <c r="E37" t="n">
-        <v>9.26444788711986</v>
+        <v>8.39423279112815</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0000000000000000000196089166588203</v>
+        <v>0.0000000000000000468946206821272</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0274096554210366</v>
+        <v>0.027325992041567</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0403301989212587</v>
+        <v>0.0423494669908353</v>
       </c>
       <c r="I37" t="n">
         <v>0.95</v>
       </c>
       <c r="J37" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1718,25 +1718,25 @@
         <v>0.0162900965612309</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00566369641122493</v>
+        <v>0.00615424040602934</v>
       </c>
       <c r="E38" t="n">
-        <v>2.87623053540537</v>
+        <v>2.64697111040243</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00402455657731445</v>
+        <v>0.00812162909758957</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00629989541372936</v>
+        <v>0.00335561297910515</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0281358616462083</v>
+        <v>0.0286056818237283</v>
       </c>
       <c r="I38" t="n">
         <v>0.95</v>
       </c>
       <c r="J38" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1753,25 +1753,25 @@
         <v>-0.00201655448013728</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0050391851714093</v>
+        <v>0.00490352961718992</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.400174713082297</v>
+        <v>-0.411245498154636</v>
       </c>
       <c r="F39" t="n">
-        <v>0.68902783805377</v>
+        <v>0.680892529253707</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.00932707128993037</v>
+        <v>-0.0103263931734672</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00902506480558917</v>
+        <v>0.00863236165926224</v>
       </c>
       <c r="I39" t="n">
         <v>0.95</v>
       </c>
       <c r="J39" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1788,25 +1788,25 @@
         <v>0.0220292719653812</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00582763593957429</v>
+        <v>0.00530372034603944</v>
       </c>
       <c r="E40" t="n">
-        <v>3.78013866923034</v>
+        <v>4.15355081491649</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000156741037564111</v>
+        <v>0.0000327355475679591</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0104974187379792</v>
+        <v>0.0120095829280971</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0305628247403827</v>
+        <v>0.0310259243611946</v>
       </c>
       <c r="I40" t="n">
         <v>0.95</v>
       </c>
       <c r="J40" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1823,25 +1823,25 @@
         <v>-0.059066507580658</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00734509276490722</v>
+        <v>0.00644791345030532</v>
       </c>
       <c r="E41" t="n">
-        <v>-8.04162853638297</v>
+        <v>-9.1605614802198</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00000000000000088652287746359</v>
+        <v>0.0000000000000000000516279849503082</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0721897687214247</v>
+        <v>-0.0716690975121771</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0492319919797971</v>
+        <v>-0.0483288012341163</v>
       </c>
       <c r="I41" t="n">
         <v>0.95</v>
       </c>
       <c r="J41" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1858,25 +1858,25 @@
         <v>-0.0737771942642836</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00839220567503477</v>
+        <v>0.00840767702902724</v>
       </c>
       <c r="E42" t="n">
-        <v>-8.79115659471465</v>
+        <v>-8.77497958229963</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00000000000000000148028071163594</v>
+        <v>0.0000000000000000017093487685667</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0873012005074596</v>
+        <v>-0.0890892205191854</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.0588268424123378</v>
+        <v>-0.0563355796037002</v>
       </c>
       <c r="I42" t="n">
         <v>0.95</v>
       </c>
       <c r="J42" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -1893,25 +1893,25 @@
         <v>0.0509023591794333</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0044753557230935</v>
+        <v>0.00479923650523745</v>
       </c>
       <c r="E43" t="n">
-        <v>11.3739247400535</v>
+        <v>10.606345222596</v>
       </c>
       <c r="F43" t="n">
-        <v>0.00000000000000000000000000000563935666345214</v>
+        <v>0.000000000000000000000000027842797558608</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0440311524547444</v>
+        <v>0.0423625076593329</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0597843186099007</v>
+        <v>0.0603909040658012</v>
       </c>
       <c r="I43" t="n">
         <v>0.95</v>
       </c>
       <c r="J43" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
